--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -746,7 +746,7 @@
         <v>3300</v>
       </c>
       <c r="E8" s="3">
-        <v>3300</v>
+        <v>6600</v>
       </c>
       <c r="F8" s="3">
         <v>3400</v>
@@ -796,7 +796,7 @@
         <v>2100</v>
       </c>
       <c r="E9" s="3">
-        <v>2300</v>
+        <v>4300</v>
       </c>
       <c r="F9" s="3">
         <v>2000</v>
@@ -846,7 +846,7 @@
         <v>1200</v>
       </c>
       <c r="E10" s="3">
-        <v>1000</v>
+        <v>2300</v>
       </c>
       <c r="F10" s="3">
         <v>1400</v>
@@ -1129,11 +1129,11 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>5700</v>
       </c>
       <c r="E17" s="3">
-        <v>6000</v>
+        <v>11800</v>
       </c>
       <c r="F17" s="3">
         <v>5700</v>
@@ -1179,11 +1179,11 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
-        <v>-2700</v>
+        <v>-5200</v>
       </c>
       <c r="F18" s="3">
         <v>-2300</v>
@@ -1249,11 +1249,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1299,11 +1299,11 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-2000</v>
       </c>
       <c r="E21" s="3">
-        <v>-2700</v>
+        <v>-4800</v>
       </c>
       <c r="F21" s="3">
         <v>-2100</v>
@@ -1353,7 +1353,7 @@
         <v>500</v>
       </c>
       <c r="E22" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F22" s="3">
         <v>300</v>
@@ -1403,7 +1403,7 @@
         <v>-2700</v>
       </c>
       <c r="E23" s="3">
-        <v>-3300</v>
+        <v>-5900</v>
       </c>
       <c r="F23" s="3">
         <v>-2600</v>
@@ -1553,7 +1553,7 @@
         <v>-2700</v>
       </c>
       <c r="E26" s="3">
-        <v>-3300</v>
+        <v>-6000</v>
       </c>
       <c r="F26" s="3">
         <v>-2700</v>
@@ -1603,7 +1603,7 @@
         <v>-2700</v>
       </c>
       <c r="E27" s="3">
-        <v>-3300</v>
+        <v>-6000</v>
       </c>
       <c r="F27" s="3">
         <v>-2700</v>
@@ -1703,7 +1703,7 @@
         <v>-100</v>
       </c>
       <c r="E29" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="F29" s="3">
         <v>-100</v>
@@ -1849,11 +1849,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>-2800</v>
       </c>
       <c r="E33" s="3">
-        <v>-3400</v>
+        <v>-6300</v>
       </c>
       <c r="F33" s="3">
         <v>-2800</v>
@@ -2003,7 +2003,7 @@
         <v>-2800</v>
       </c>
       <c r="E35" s="3">
-        <v>-3400</v>
+        <v>-6300</v>
       </c>
       <c r="F35" s="3">
         <v>-2800</v>
@@ -2245,7 +2245,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="E43" s="3">
         <v>1600</v>
@@ -2884,8 +2884,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>2600</v>
       </c>
       <c r="E57" s="3">
         <v>2400</v>
@@ -2935,7 +2935,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9800</v>
+        <v>14200</v>
       </c>
       <c r="E58" s="3">
         <v>9900</v>
@@ -3963,7 +3963,7 @@
         <v>-2800</v>
       </c>
       <c r="E81" s="3">
-        <v>-3400</v>
+        <v>-6300</v>
       </c>
       <c r="F81" s="3">
         <v>-2800</v>
@@ -4033,7 +4033,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -4333,7 +4333,7 @@
         <v>18300</v>
       </c>
       <c r="E89" s="3">
-        <v>2900</v>
+        <v>-12000</v>
       </c>
       <c r="F89" s="3">
         <v>-15000</v>
@@ -4553,7 +4553,7 @@
         <v>-400</v>
       </c>
       <c r="E94" s="3">
-        <v>-200</v>
+        <v>-500</v>
       </c>
       <c r="F94" s="3">
         <v>-200</v>
@@ -4819,11 +4819,11 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>3500</v>
       </c>
       <c r="E100" s="3">
-        <v>100</v>
+        <v>4400</v>
       </c>
       <c r="F100" s="3">
         <v>4200</v>
@@ -4923,7 +4923,7 @@
         <v>21400</v>
       </c>
       <c r="E102" s="3">
-        <v>2800</v>
+        <v>-8100</v>
       </c>
       <c r="F102" s="3">
         <v>-11000</v>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,124 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43921</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="3">
         <v>3300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6600</v>
       </c>
-      <c r="F8" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2600</v>
       </c>
       <c r="O8" s="3">
         <v>1200</v>
@@ -782,45 +789,51 @@
         <v>2600</v>
       </c>
       <c r="Q8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S8" s="3">
         <v>3000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F9" s="3">
         <v>2100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4300</v>
       </c>
-      <c r="F9" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2700</v>
-      </c>
       <c r="H9" s="3">
+        <v>800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J9" s="3">
         <v>3400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2900</v>
-      </c>
-      <c r="J9" s="3">
-        <v>900</v>
-      </c>
-      <c r="K9" s="3">
-        <v>900</v>
       </c>
       <c r="L9" s="3">
         <v>900</v>
       </c>
       <c r="M9" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="N9" s="3">
         <v>900</v>
@@ -829,66 +842,78 @@
         <v>500</v>
       </c>
       <c r="P9" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>500</v>
+      </c>
+      <c r="R9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>900</v>
-      </c>
       <c r="H10" s="3">
+        <v>400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1700</v>
       </c>
       <c r="O10" s="3">
         <v>700</v>
       </c>
       <c r="P10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>700</v>
+      </c>
+      <c r="R10" s="3">
         <v>1600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -907,8 +932,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -942,23 +969,29 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
-        <v>300</v>
-      </c>
-      <c r="O12" s="3">
-        <v>100</v>
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P12" s="3">
         <v>300</v>
       </c>
       <c r="Q12" s="3">
+        <v>100</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
+        <v>300</v>
+      </c>
+      <c r="T12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1007,16 +1040,22 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1025,26 +1064,26 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>4700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K14" s="3">
         <v>26200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1057,8 +1096,14 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1107,8 +1152,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,108 +1175,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="E17" s="3">
-        <v>11800</v>
+        <v>13800</v>
       </c>
       <c r="F17" s="3">
         <v>5700</v>
       </c>
       <c r="G17" s="3">
-        <v>8600</v>
+        <v>11800</v>
       </c>
       <c r="H17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>17800</v>
+      </c>
+      <c r="J17" s="3">
         <v>14100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>57100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-10500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-54700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,8 +1309,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1253,19 +1320,19 @@
         <v>200</v>
       </c>
       <c r="E20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>200</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1294,38 +1361,44 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4800</v>
       </c>
-      <c r="F21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-9900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-54400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1344,32 +1417,38 @@
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
-        <v>300</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1382,11 +1461,11 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1394,58 +1473,70 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5900</v>
       </c>
-      <c r="F23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-4700</v>
-      </c>
       <c r="H23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-10600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-54700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1471,31 +1562,37 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1641,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2700</v>
+        <v>-1800</v>
       </c>
       <c r="E26" s="3">
-        <v>-6000</v>
+        <v>-11200</v>
       </c>
       <c r="F26" s="3">
         <v>-2700</v>
       </c>
       <c r="G26" s="3">
-        <v>-4700</v>
+        <v>-6000</v>
       </c>
       <c r="H26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-10600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-54700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2700</v>
+        <v>-1800</v>
       </c>
       <c r="E27" s="3">
-        <v>-6000</v>
+        <v>-11200</v>
       </c>
       <c r="F27" s="3">
         <v>-2700</v>
       </c>
       <c r="G27" s="3">
-        <v>-4700</v>
+        <v>-6000</v>
       </c>
       <c r="H27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-10600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-54700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,32 +1809,38 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-100</v>
+        <v>14100</v>
       </c>
       <c r="E29" s="3">
-        <v>-300</v>
+        <v>-3000</v>
       </c>
       <c r="F29" s="3">
         <v>-100</v>
       </c>
       <c r="G29" s="3">
-        <v>1300</v>
+        <v>-300</v>
       </c>
       <c r="H29" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1300</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -1730,22 +1851,28 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>100</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1921,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,8 +1977,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1853,19 +1992,19 @@
         <v>-200</v>
       </c>
       <c r="E32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1894,58 +2033,70 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2800</v>
+        <v>12400</v>
       </c>
       <c r="E33" s="3">
-        <v>-6300</v>
+        <v>-14200</v>
       </c>
       <c r="F33" s="3">
         <v>-2800</v>
       </c>
       <c r="G33" s="3">
-        <v>-3400</v>
+        <v>-6300</v>
       </c>
       <c r="H33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-11800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-54700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-200</v>
-      </c>
       <c r="Q33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R33" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2145,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2800</v>
+        <v>12400</v>
       </c>
       <c r="E35" s="3">
-        <v>-6300</v>
+        <v>-14200</v>
       </c>
       <c r="F35" s="3">
         <v>-2800</v>
       </c>
       <c r="G35" s="3">
-        <v>-3400</v>
+        <v>-6300</v>
       </c>
       <c r="H35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-11800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-54700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-200</v>
-      </c>
       <c r="Q35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43921</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2288,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,58 +2310,66 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F41" s="3">
         <v>49300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>31900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>28800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>39300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2239,58 +2418,70 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>600</v>
-      </c>
-      <c r="K43" s="3">
-        <v>800</v>
       </c>
       <c r="L43" s="3">
         <v>600</v>
       </c>
       <c r="M43" s="3">
+        <v>800</v>
+      </c>
+      <c r="N43" s="3">
+        <v>600</v>
+      </c>
+      <c r="O43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1300</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2339,116 +2530,134 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>68200</v>
+      </c>
+      <c r="F45" s="3">
         <v>22400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>15200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>18000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>13500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>71100</v>
+      </c>
+      <c r="F46" s="3">
         <v>73300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>48700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>48900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>53900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3500</v>
-      </c>
-      <c r="M46" s="3">
-        <v>3200</v>
-      </c>
-      <c r="N46" s="3">
-        <v>4100</v>
       </c>
       <c r="O46" s="3">
         <v>3200</v>
       </c>
       <c r="P46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>3200</v>
+      </c>
+      <c r="R46" s="3">
         <v>3600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>200</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
         <v>200</v>
@@ -2462,11 +2671,11 @@
       <c r="I47" s="3">
         <v>200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>200</v>
+      </c>
+      <c r="K47" s="3">
+        <v>200</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -2474,31 +2683,37 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>500</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
@@ -2507,25 +2722,25 @@
         <v>300</v>
       </c>
       <c r="H48" s="3">
+        <v>300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>300</v>
+      </c>
+      <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>100</v>
@@ -2536,61 +2751,73 @@
       <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>100</v>
+      </c>
+      <c r="S48" s="3">
+        <v>100</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>200</v>
+      </c>
+      <c r="F49" s="3">
         <v>10900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>10700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>10700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>10600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>10300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2600</v>
-      </c>
-      <c r="M49" s="3">
-        <v>3200</v>
-      </c>
-      <c r="N49" s="3">
-        <v>3200</v>
       </c>
       <c r="O49" s="3">
         <v>3200</v>
       </c>
       <c r="P49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="R49" s="3">
         <v>3500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3500</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2866,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,16 +2922,22 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
@@ -2706,30 +2945,30 @@
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
       </c>
       <c r="M52" s="3">
+        <v>400</v>
+      </c>
+      <c r="N52" s="3">
+        <v>400</v>
+      </c>
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2739,8 +2978,14 @@
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,58 +3034,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>71300</v>
+      </c>
+      <c r="F54" s="3">
         <v>84700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>59900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>60100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>65000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>8000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>7100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>7700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +3116,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,37 +3138,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -2921,40 +3182,46 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F58" s="3">
         <v>14200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>9900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3400</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
@@ -2967,11 +3234,11 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -2979,129 +3246,147 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>66400</v>
+      </c>
+      <c r="F59" s="3">
         <v>70100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>46800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>45000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>51600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2700</v>
       </c>
       <c r="M59" s="3">
         <v>3000</v>
       </c>
       <c r="N59" s="3">
-        <v>3800</v>
+        <v>2700</v>
       </c>
       <c r="O59" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="P59" s="3">
         <v>3800</v>
       </c>
       <c r="Q59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="R59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>79200</v>
+      </c>
+      <c r="F60" s="3">
         <v>86800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>59000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>55700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>58900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3300</v>
-      </c>
-      <c r="K60" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2800</v>
       </c>
       <c r="M60" s="3">
         <v>3100</v>
       </c>
       <c r="N60" s="3">
-        <v>3900</v>
+        <v>2800</v>
       </c>
       <c r="O60" s="3">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="P60" s="3">
         <v>3900</v>
       </c>
       <c r="Q60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="S60" s="3">
         <v>4200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F61" s="3">
         <v>2100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -3129,16 +3414,22 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
@@ -3147,40 +3438,46 @@
         <v>200</v>
       </c>
       <c r="H62" s="3">
+        <v>200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>200</v>
+      </c>
+      <c r="J62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>1000</v>
       </c>
       <c r="P62" s="3">
         <v>1000</v>
       </c>
       <c r="Q62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3526,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3582,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,58 +3638,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>80700</v>
+      </c>
+      <c r="F66" s="3">
         <v>89200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>61700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>58600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>62100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3700</v>
-      </c>
-      <c r="N66" s="3">
-        <v>4900</v>
-      </c>
-      <c r="O66" s="3">
-        <v>4300</v>
       </c>
       <c r="P66" s="3">
         <v>4900</v>
       </c>
       <c r="Q66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="R66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="S66" s="3">
         <v>5100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3720,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3772,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3828,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3884,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,58 +3940,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-87900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-82700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-79900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-76400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-73600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-70200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-58300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-30400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-29400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-28200</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-27600</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-27500</v>
       </c>
       <c r="O72" s="3">
         <v>-27600</v>
       </c>
       <c r="P72" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="S72" s="3">
         <v>-27400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +4052,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +4108,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,58 +4164,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-4500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2400</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4276,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43921</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2800</v>
+        <v>12400</v>
       </c>
       <c r="E81" s="3">
-        <v>-6300</v>
+        <v>-14200</v>
       </c>
       <c r="F81" s="3">
         <v>-2800</v>
       </c>
       <c r="G81" s="3">
-        <v>-3400</v>
+        <v>-6300</v>
       </c>
       <c r="H81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-11800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-54700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-200</v>
-      </c>
       <c r="Q81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R81" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,37 +4419,39 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
+        <v>400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="H83" s="3">
-        <v>600</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
@@ -4068,14 +4465,20 @@
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4527,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4583,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4639,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4695,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,38 +4751,44 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>600</v>
+      </c>
+      <c r="F89" s="3">
         <v>18300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-12000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-15000</v>
       </c>
-      <c r="G89" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>8</v>
       </c>
@@ -4368,14 +4801,20 @@
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,43 +4833,45 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>8</v>
@@ -4438,14 +4879,20 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4941,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,37 +4997,43 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
-        <v>48800</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>48300</v>
+      </c>
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4400</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
@@ -4588,14 +5047,20 @@
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,8 +5079,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4664,8 +5131,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +5187,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5243,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,37 +5299,43 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F100" s="3">
         <v>3500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>4200</v>
       </c>
-      <c r="G100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>15700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
@@ -4855,17 +5346,23 @@
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4914,38 +5411,44 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F102" s="3">
         <v>21400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-11000</v>
       </c>
-      <c r="G102" s="3">
-        <v>46100</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>45000</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>8</v>
       </c>
@@ -4958,10 +5461,16 @@
       <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,96 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -753,55 +757,58 @@
         <v>1000</v>
       </c>
       <c r="E8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="3">
         <v>5000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3300</v>
       </c>
-      <c r="G8" s="3">
-        <v>6600</v>
-      </c>
       <c r="H8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I8" s="3">
         <v>1200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,28 +816,28 @@
         <v>700</v>
       </c>
       <c r="E9" s="3">
+        <v>700</v>
+      </c>
+      <c r="F9" s="3">
         <v>3400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2100</v>
       </c>
-      <c r="G9" s="3">
-        <v>4300</v>
-      </c>
       <c r="H9" s="3">
+        <v>900</v>
+      </c>
+      <c r="I9" s="3">
         <v>800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2900</v>
-      </c>
-      <c r="L9" s="3">
-        <v>900</v>
       </c>
       <c r="M9" s="3">
         <v>900</v>
@@ -839,25 +846,28 @@
         <v>900</v>
       </c>
       <c r="O9" s="3">
+        <v>900</v>
+      </c>
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1000</v>
       </c>
       <c r="S9" s="3">
         <v>1000</v>
       </c>
       <c r="T9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,55 +875,58 @@
         <v>300</v>
       </c>
       <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2300</v>
       </c>
       <c r="H10" s="3">
         <v>400</v>
       </c>
       <c r="I10" s="3">
+        <v>400</v>
+      </c>
+      <c r="J10" s="3">
         <v>1300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,8 +947,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,23 +989,26 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>100</v>
-      </c>
-      <c r="R12" s="3">
-        <v>300</v>
       </c>
       <c r="S12" s="3">
         <v>300</v>
       </c>
       <c r="T12" s="3">
+        <v>300</v>
+      </c>
+      <c r="U12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,20 +1063,23 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1067,26 +1087,26 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4700</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>4700</v>
       </c>
       <c r="K14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L14" s="3">
         <v>26200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1102,8 +1122,11 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1158,8 +1181,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1203,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5700</v>
       </c>
-      <c r="G17" s="3">
-        <v>11800</v>
-      </c>
       <c r="H17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I17" s="3">
         <v>2900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-54700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
         <v>0</v>
       </c>
       <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,32 +1344,33 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1367,41 +1401,44 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-54400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1423,34 +1460,37 @@
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>700</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
+      <c r="K22" s="3">
+        <v>100</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
@@ -1467,8 +1507,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1479,64 +1519,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5900</v>
-      </c>
       <c r="H23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-54700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1568,16 +1614,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1586,13 +1632,16 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,47 +1696,50 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2700</v>
       </c>
-      <c r="G26" s="3">
-        <v>-6000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-54700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
@@ -1695,55 +1747,58 @@
         <v>0</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-6000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-54700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
@@ -1751,16 +1806,19 @@
         <v>0</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,35 +1873,38 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>500</v>
+      </c>
+      <c r="E29" s="3">
         <v>14100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-3000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
-        <v>-300</v>
-      </c>
       <c r="H29" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I29" s="3">
         <v>-800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-1100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-1300</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -1857,22 +1918,25 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>100</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1991,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,32 +2050,35 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
       <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2039,64 +2109,70 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12400</v>
+        <v>-500</v>
       </c>
       <c r="E33" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-14200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2800</v>
       </c>
-      <c r="G33" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-54700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2227,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12400</v>
+        <v>-500</v>
       </c>
       <c r="E35" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-14200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2800</v>
       </c>
-      <c r="G35" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-54700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2375,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,64 +2398,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E41" s="3">
         <v>4000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>39300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1600</v>
-      </c>
-      <c r="P41" s="3">
-        <v>1700</v>
       </c>
       <c r="Q41" s="3">
         <v>1700</v>
       </c>
       <c r="R41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S41" s="3">
         <v>1600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,64 +2514,70 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
         <v>400</v>
       </c>
       <c r="F43" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="G43" s="3">
         <v>1600</v>
       </c>
       <c r="H43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I43" s="3">
         <v>2100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
-      </c>
-      <c r="O43" s="3">
-        <v>700</v>
       </c>
       <c r="P43" s="3">
         <v>700</v>
       </c>
       <c r="Q43" s="3">
+        <v>700</v>
+      </c>
+      <c r="R43" s="3">
         <v>600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2536,120 +2632,129 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>68200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1600</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E46" s="3">
         <v>5400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>71100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>73300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>48700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>48900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>53900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2700</v>
-      </c>
-      <c r="M46" s="3">
-        <v>3500</v>
       </c>
       <c r="N46" s="3">
         <v>3500</v>
       </c>
       <c r="O46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P46" s="3">
         <v>3200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2659,8 +2764,8 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
-        <v>200</v>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
         <v>200</v>
@@ -2677,8 +2782,8 @@
       <c r="K47" s="3">
         <v>200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
+      <c r="L47" s="3">
+        <v>200</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
@@ -2689,23 +2794,26 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>700</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>600</v>
       </c>
       <c r="R47" s="3">
         <v>600</v>
       </c>
       <c r="S47" s="3">
+        <v>600</v>
+      </c>
+      <c r="T47" s="3">
         <v>500</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2716,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <v>300</v>
@@ -2728,13 +2836,13 @@
         <v>300</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2743,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3">
         <v>100</v>
@@ -2757,11 +2865,14 @@
       <c r="S48" s="3">
         <v>100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>100</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2769,37 +2880,37 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>10700</v>
       </c>
       <c r="H49" s="3">
         <v>10700</v>
       </c>
       <c r="I49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J49" s="3">
         <v>10600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10300</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1500</v>
       </c>
       <c r="M49" s="3">
         <v>1500</v>
       </c>
       <c r="N49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O49" s="3">
         <v>2600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>3200</v>
       </c>
       <c r="P49" s="3">
         <v>3200</v>
@@ -2808,16 +2919,19 @@
         <v>3200</v>
       </c>
       <c r="R49" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="S49" s="3">
         <v>3500</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2986,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,19 +3045,22 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
@@ -2951,14 +3071,14 @@
       <c r="I52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
-        <v>300</v>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
       </c>
       <c r="L52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
@@ -2967,11 +3087,11 @@
         <v>400</v>
       </c>
       <c r="O52" s="3">
+        <v>400</v>
+      </c>
+      <c r="P52" s="3">
         <v>300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2984,8 +3104,11 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3163,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>84700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>59900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>60100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>65000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3247,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,40 +3270,41 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -3188,16 +3319,19 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>200</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3205,26 +3339,26 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>11400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3240,8 +3374,8 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3252,120 +3386,129 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>66400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>70100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>45000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>79200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>86800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>59000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>58900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3373,23 +3516,23 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>1400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3420,8 +3563,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3432,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
@@ -3444,25 +3590,25 @@
         <v>200</v>
       </c>
       <c r="J62" s="3">
+        <v>200</v>
+      </c>
+      <c r="K62" s="3">
         <v>2800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>300</v>
       </c>
       <c r="M62" s="3">
         <v>300</v>
       </c>
       <c r="N62" s="3">
+        <v>300</v>
+      </c>
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1000</v>
       </c>
       <c r="Q62" s="3">
         <v>1000</v>
@@ -3471,13 +3617,16 @@
         <v>1000</v>
       </c>
       <c r="S62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3681,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3740,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,64 +3799,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>89200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>58600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>62100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3883,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3940,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3999,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4058,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,64 +4117,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-75600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-87900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-82700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-79900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-76400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-73600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-70200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-58300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-29400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-28200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-27500</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-27600</v>
       </c>
       <c r="R72" s="3">
         <v>-27600</v>
       </c>
       <c r="S72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="T72" s="3">
         <v>-27400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4235,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4294,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4353,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-9400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-4500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3200</v>
-      </c>
-      <c r="O76" s="3">
-        <v>3100</v>
       </c>
       <c r="P76" s="3">
         <v>3100</v>
       </c>
       <c r="Q76" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="R76" s="3">
         <v>2800</v>
       </c>
       <c r="S76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="T76" s="3">
         <v>2400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4471,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12400</v>
+        <v>-500</v>
       </c>
       <c r="E81" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-14200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2800</v>
       </c>
-      <c r="G81" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-54700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,8 +4619,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4430,31 +4629,31 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>400</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
@@ -4471,14 +4670,17 @@
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4735,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4794,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4853,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4912,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,41 +4971,44 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-12000</v>
-      </c>
       <c r="H89" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-15000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>8</v>
       </c>
@@ -4807,14 +5024,17 @@
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,8 +5055,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4844,37 +5065,37 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>8</v>
@@ -4885,14 +5106,17 @@
       <c r="R91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5171,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,40 +5230,43 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-500</v>
       </c>
       <c r="H94" s="3">
         <v>-200</v>
       </c>
       <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>48300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
@@ -5053,14 +5283,17 @@
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5314,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5137,8 +5371,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5430,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5489,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,40 +5548,43 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3500</v>
       </c>
-      <c r="G100" s="3">
-        <v>4400</v>
-      </c>
       <c r="H100" s="3">
+        <v>100</v>
+      </c>
+      <c r="I100" s="3">
         <v>4200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>15700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
@@ -5352,8 +5598,8 @@
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -5361,8 +5607,11 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5417,41 +5666,44 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-56200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21400</v>
       </c>
-      <c r="G102" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-11000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>45000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5467,10 +5719,13 @@
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,159 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E8" s="3">
         <v>1000</v>
       </c>
       <c r="F8" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3300</v>
+        <v>1000</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H8" s="3">
         <v>1300</v>
       </c>
       <c r="I8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,28 +826,28 @@
         <v>700</v>
       </c>
       <c r="F9" s="3">
+        <v>700</v>
+      </c>
+      <c r="G9" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>800</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L9" s="3">
         <v>3400</v>
       </c>
-      <c r="G9" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>800</v>
-      </c>
-      <c r="J9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3400</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2900</v>
-      </c>
-      <c r="M9" s="3">
-        <v>900</v>
       </c>
       <c r="N9" s="3">
         <v>900</v>
@@ -849,39 +856,42 @@
         <v>900</v>
       </c>
       <c r="P9" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>500</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1000</v>
       </c>
       <c r="T9" s="3">
         <v>1000</v>
       </c>
       <c r="U9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>300</v>
       </c>
       <c r="F10" s="3">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="G10" s="3">
-        <v>1200</v>
+        <v>-1900</v>
       </c>
       <c r="H10" s="3">
         <v>400</v>
@@ -890,43 +900,46 @@
         <v>400</v>
       </c>
       <c r="J10" s="3">
+        <v>400</v>
+      </c>
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +961,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -992,23 +1006,26 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>100</v>
-      </c>
-      <c r="S12" s="3">
-        <v>300</v>
       </c>
       <c r="T12" s="3">
         <v>300</v>
       </c>
       <c r="U12" s="3">
+        <v>300</v>
+      </c>
+      <c r="V12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1066,50 +1083,53 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>2500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>4700</v>
+        <v>400</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>4700</v>
       </c>
       <c r="L14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M14" s="3">
         <v>26200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1125,8 +1145,11 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1140,16 +1163,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1184,8 +1207,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1204,126 +1230,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2700</v>
       </c>
-      <c r="F17" s="3">
-        <v>13800</v>
-      </c>
       <c r="G17" s="3">
-        <v>5700</v>
+        <v>-6100</v>
       </c>
       <c r="H17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I17" s="3">
         <v>3100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-8800</v>
-      </c>
       <c r="G18" s="3">
-        <v>-2400</v>
+        <v>1100</v>
       </c>
       <c r="H18" s="3">
-        <v>-1800</v>
+        <v>-1400</v>
       </c>
       <c r="I18" s="3">
         <v>-1700</v>
       </c>
       <c r="J18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-14300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1345,34 +1378,35 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>200</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
-        <v>-1200</v>
+        <v>-200</v>
       </c>
       <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-200</v>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
         <v>300</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1404,44 +1438,47 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-10000</v>
-      </c>
       <c r="G21" s="3">
-        <v>-2000</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="3">
-        <v>-2000</v>
+        <v>-1300</v>
       </c>
       <c r="I21" s="3">
         <v>-1700</v>
       </c>
       <c r="J21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-12800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-54400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1463,37 +1500,40 @@
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
-        <v>1200</v>
-      </c>
       <c r="G22" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
+      <c r="L22" s="3">
+        <v>100</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
@@ -1510,8 +1550,8 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1522,67 +1562,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
-        <v>-11200</v>
-      </c>
       <c r="G23" s="3">
-        <v>-2700</v>
+        <v>-2600</v>
       </c>
       <c r="H23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-54700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1617,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1635,13 +1681,16 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1699,50 +1748,53 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-11200</v>
-      </c>
       <c r="G26" s="3">
-        <v>-2700</v>
+        <v>-2600</v>
       </c>
       <c r="H26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-54700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
@@ -1750,16 +1802,19 @@
         <v>0</v>
       </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1767,41 +1822,41 @@
         <v>-900</v>
       </c>
       <c r="E27" s="3">
-        <v>-1800</v>
+        <v>-500</v>
       </c>
       <c r="F27" s="3">
-        <v>-11200</v>
+        <v>12300</v>
       </c>
       <c r="G27" s="3">
-        <v>-2700</v>
+        <v>-5100</v>
       </c>
       <c r="H27" s="3">
-        <v>-2500</v>
+        <v>-2800</v>
       </c>
       <c r="I27" s="3">
-        <v>-2200</v>
+        <v>-3500</v>
       </c>
       <c r="J27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-14100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-54700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
@@ -1809,16 +1864,19 @@
         <v>0</v>
       </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1876,38 +1934,41 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3">
         <v>500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>14100</v>
       </c>
-      <c r="F29" s="3">
-        <v>-3000</v>
-      </c>
       <c r="G29" s="3">
-        <v>-100</v>
+        <v>-2600</v>
       </c>
       <c r="H29" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K29" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1300</v>
       </c>
-      <c r="I29" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K29" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -1921,22 +1982,25 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>100</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1994,8 +2058,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2053,34 +2120,37 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-200</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>200</v>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
         <v>-300</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2112,67 +2182,73 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
-        <v>12300</v>
-      </c>
       <c r="F33" s="3">
-        <v>-14200</v>
+        <v>12400</v>
       </c>
       <c r="G33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H33" s="3">
         <v>-2800</v>
       </c>
-      <c r="H33" s="3">
-        <v>-3800</v>
-      </c>
       <c r="I33" s="3">
-        <v>-3000</v>
+        <v>-3400</v>
       </c>
       <c r="J33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-15200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-54700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2230,131 +2306,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
-        <v>12300</v>
-      </c>
       <c r="F35" s="3">
-        <v>-14200</v>
+        <v>12400</v>
       </c>
       <c r="G35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H35" s="3">
         <v>-2800</v>
       </c>
-      <c r="H35" s="3">
-        <v>-3800</v>
-      </c>
       <c r="I35" s="3">
-        <v>-3000</v>
+        <v>-3400</v>
       </c>
       <c r="J35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-15200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-54700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2376,8 +2461,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,67 +2485,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>1700</v>
       </c>
       <c r="R41" s="3">
         <v>1700</v>
       </c>
       <c r="S41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T41" s="3">
         <v>1600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2517,90 +2607,96 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
-      </c>
-      <c r="E43" s="3">
-        <v>400</v>
       </c>
       <c r="F43" s="3">
         <v>400</v>
       </c>
       <c r="G43" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>1600</v>
       </c>
       <c r="I43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J43" s="3">
         <v>2100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
-      </c>
-      <c r="P43" s="3">
-        <v>700</v>
       </c>
       <c r="Q43" s="3">
         <v>700</v>
       </c>
       <c r="R43" s="3">
+        <v>700</v>
+      </c>
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1300</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2635,126 +2731,135 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3">
+        <v>67800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="L45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N45" s="3">
+        <v>900</v>
+      </c>
+      <c r="O45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>68200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>22400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>18000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>13500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
+        <v>800</v>
+      </c>
+      <c r="R45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="T45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3">
-        <v>900</v>
-      </c>
-      <c r="S45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>71100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>73300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>48700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>53900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2700</v>
-      </c>
-      <c r="N46" s="3">
-        <v>3500</v>
       </c>
       <c r="O46" s="3">
         <v>3500</v>
       </c>
       <c r="P46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q46" s="3">
         <v>3200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2767,8 +2872,8 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>200</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
         <v>200</v>
@@ -2785,8 +2890,8 @@
       <c r="L47" s="3">
         <v>200</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
+      <c r="M47" s="3">
+        <v>200</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -2797,23 +2902,26 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>700</v>
-      </c>
-      <c r="R47" s="3">
-        <v>600</v>
       </c>
       <c r="S47" s="3">
         <v>600</v>
       </c>
       <c r="T47" s="3">
+        <v>600</v>
+      </c>
+      <c r="U47" s="3">
         <v>500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2827,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
@@ -2839,13 +2947,13 @@
         <v>300</v>
       </c>
       <c r="K48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2854,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3">
         <v>100</v>
@@ -2868,11 +2976,14 @@
       <c r="T48" s="3">
         <v>100</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>100</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2883,37 +2994,37 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10900</v>
-      </c>
-      <c r="H49" s="3">
-        <v>10700</v>
       </c>
       <c r="I49" s="3">
         <v>10700</v>
       </c>
       <c r="J49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K49" s="3">
         <v>10600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1500</v>
       </c>
       <c r="N49" s="3">
         <v>1500</v>
       </c>
       <c r="O49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P49" s="3">
         <v>2600</v>
-      </c>
-      <c r="P49" s="3">
-        <v>3200</v>
       </c>
       <c r="Q49" s="3">
         <v>3200</v>
@@ -2922,16 +3033,19 @@
         <v>3200</v>
       </c>
       <c r="S49" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="T49" s="3">
         <v>3500</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3103,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3048,8 +3165,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3059,8 +3179,8 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
@@ -3074,14 +3194,14 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>300</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
       </c>
       <c r="M52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
@@ -3090,11 +3210,11 @@
         <v>400</v>
       </c>
       <c r="P52" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3107,8 +3227,11 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3166,67 +3289,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>84700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>59900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>60100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>65000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7500</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3248,8 +3377,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3271,8 +3401,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3280,34 +3411,34 @@
         <v>700</v>
       </c>
       <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
-        <v>1500</v>
-      </c>
       <c r="G57" s="3">
+        <v>800</v>
+      </c>
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
-        <v>1900</v>
-      </c>
       <c r="J57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -3322,16 +3453,19 @@
         <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>200</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3342,26 +3476,26 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>11400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3400</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3377,8 +3511,8 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3389,126 +3523,135 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>66400</v>
       </c>
-      <c r="G59" s="3">
-        <v>70100</v>
-      </c>
       <c r="H59" s="3">
-        <v>46800</v>
+        <v>58400</v>
       </c>
       <c r="I59" s="3">
-        <v>45000</v>
+        <v>40900</v>
       </c>
       <c r="J59" s="3">
+        <v>38800</v>
+      </c>
+      <c r="K59" s="3">
         <v>51600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>79200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>86800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3519,22 +3662,22 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>1400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>2100</v>
       </c>
       <c r="H61" s="3">
         <v>2400</v>
       </c>
       <c r="I61" s="3">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="J61" s="3">
         <v>2900</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -3566,52 +3709,55 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
-        <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>200</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
-      </c>
-      <c r="M62" s="3">
-        <v>300</v>
       </c>
       <c r="N62" s="3">
         <v>300</v>
       </c>
       <c r="O62" s="3">
+        <v>300</v>
+      </c>
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1000</v>
       </c>
       <c r="R62" s="3">
         <v>1000</v>
@@ -3620,13 +3766,16 @@
         <v>1000</v>
       </c>
       <c r="T62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3684,8 +3833,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,8 +3895,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3802,67 +3957,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>80700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>89200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>62100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3884,8 +4045,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3943,8 +4105,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4002,8 +4167,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4061,8 +4229,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4120,67 +4291,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-76000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-75600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-87900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-82700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-79900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-76400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-73600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-70200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-58300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-29400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-28200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27500</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-27600</v>
       </c>
       <c r="S72" s="3">
         <v>-27600</v>
       </c>
       <c r="T72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="U72" s="3">
         <v>-27400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4238,8 +4415,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4297,8 +4477,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4356,67 +4539,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-9400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3200</v>
-      </c>
-      <c r="P76" s="3">
-        <v>3100</v>
       </c>
       <c r="Q76" s="3">
         <v>3100</v>
       </c>
       <c r="R76" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="S76" s="3">
         <v>2800</v>
       </c>
       <c r="T76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U76" s="3">
         <v>2400</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4474,131 +4663,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
-        <v>12300</v>
-      </c>
       <c r="F81" s="3">
-        <v>-14200</v>
+        <v>12400</v>
       </c>
       <c r="G81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H81" s="3">
         <v>-2800</v>
       </c>
-      <c r="H81" s="3">
-        <v>-3800</v>
-      </c>
       <c r="I81" s="3">
-        <v>-3000</v>
+        <v>-3400</v>
       </c>
       <c r="J81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-15200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-54700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4620,43 +4818,44 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
-        <v>200</v>
-      </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
@@ -4673,14 +4872,17 @@
       <c r="S83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4738,8 +4940,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4797,8 +5002,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4856,8 +5064,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5126,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4974,44 +5188,47 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1700</v>
+        <v>-600</v>
       </c>
       <c r="E89" s="3">
-        <v>-19300</v>
+        <v>-1600</v>
       </c>
       <c r="F89" s="3">
-        <v>600</v>
+        <v>-19500</v>
       </c>
       <c r="G89" s="3">
-        <v>18300</v>
+        <v>-63400</v>
       </c>
       <c r="H89" s="3">
-        <v>2900</v>
+        <v>-1000</v>
       </c>
       <c r="I89" s="3">
-        <v>-15000</v>
+        <v>-1500</v>
       </c>
       <c r="J89" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="K89" s="3">
         <v>-5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5027,14 +5244,17 @@
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5056,8 +5276,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5068,37 +5289,37 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>8</v>
@@ -5109,14 +5330,17 @@
       <c r="S91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5174,8 +5398,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5233,8 +5460,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5242,34 +5472,34 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-18700</v>
       </c>
-      <c r="F94" s="3">
-        <v>-1000</v>
-      </c>
       <c r="G94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H94" s="3">
         <v>-400</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-200</v>
       </c>
       <c r="I94" s="3">
         <v>-200</v>
       </c>
       <c r="J94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K94" s="3">
         <v>48300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
@@ -5286,14 +5516,17 @@
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5315,31 +5548,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5374,8 +5608,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5433,8 +5670,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5492,8 +5732,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5551,43 +5794,46 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18200</v>
       </c>
-      <c r="F100" s="3">
-        <v>9800</v>
-      </c>
       <c r="G100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H100" s="3">
         <v>3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
@@ -5601,8 +5847,8 @@
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -5610,31 +5856,34 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5669,44 +5918,47 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
-        <v>-56200</v>
-      </c>
       <c r="F102" s="3">
-        <v>9300</v>
+        <v>-56400</v>
       </c>
       <c r="G102" s="3">
-        <v>21400</v>
+        <v>-61700</v>
       </c>
       <c r="H102" s="3">
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="I102" s="3">
-        <v>-11000</v>
+        <v>-1600</v>
       </c>
       <c r="J102" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="K102" s="3">
         <v>45000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5722,10 +5974,13 @@
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,166 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1000</v>
       </c>
       <c r="F8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
+      <c r="G8" s="3">
+        <v>1000</v>
       </c>
       <c r="H8" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="I8" s="3">
         <v>1300</v>
       </c>
       <c r="J8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -829,28 +835,28 @@
         <v>700</v>
       </c>
       <c r="G9" s="3">
-        <v>-3100</v>
+        <v>700</v>
       </c>
       <c r="H9" s="3">
+        <v>700</v>
+      </c>
+      <c r="I9" s="3">
         <v>1000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2900</v>
-      </c>
-      <c r="N9" s="3">
-        <v>900</v>
       </c>
       <c r="O9" s="3">
         <v>900</v>
@@ -859,25 +865,28 @@
         <v>900</v>
       </c>
       <c r="Q9" s="3">
+        <v>900</v>
+      </c>
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1000</v>
       </c>
       <c r="U9" s="3">
         <v>1000</v>
       </c>
       <c r="V9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -885,13 +894,13 @@
         <v>200</v>
       </c>
       <c r="E10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>300</v>
       </c>
       <c r="G10" s="3">
-        <v>-1900</v>
+        <v>300</v>
       </c>
       <c r="H10" s="3">
         <v>400</v>
@@ -903,43 +912,46 @@
         <v>400</v>
       </c>
       <c r="K10" s="3">
+        <v>400</v>
+      </c>
+      <c r="L10" s="3">
         <v>1300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1009,23 +1022,26 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>100</v>
-      </c>
-      <c r="T12" s="3">
-        <v>300</v>
       </c>
       <c r="U12" s="3">
         <v>300</v>
       </c>
       <c r="V12" s="3">
+        <v>300</v>
+      </c>
+      <c r="W12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1086,53 +1102,56 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2500</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>4700</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>4700</v>
       </c>
       <c r="M14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N14" s="3">
         <v>26200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1148,8 +1167,11 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1163,20 +1185,20 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1210,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1231,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2700</v>
       </c>
-      <c r="G17" s="3">
-        <v>-6100</v>
-      </c>
       <c r="H17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I17" s="3">
         <v>2800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>57100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
-        <v>1100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1700</v>
       </c>
       <c r="J18" s="3">
         <v>-1700</v>
       </c>
       <c r="K18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L18" s="3">
         <v>-14300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-54700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1379,37 +1411,38 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-300</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>200</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
-        <v>300</v>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>300</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1441,8 +1474,11 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1450,38 +1486,38 @@
         <v>-800</v>
       </c>
       <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
-        <v>1000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-54400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1503,40 +1539,43 @@
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
+      <c r="M22" s="3">
+        <v>100</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
@@ -1553,8 +1592,8 @@
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1565,75 +1604,81 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1666,16 +1711,16 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1684,13 +1729,16 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1751,53 +1799,56 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
@@ -1805,16 +1856,19 @@
         <v>0</v>
       </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1822,44 +1876,44 @@
         <v>-900</v>
       </c>
       <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
@@ -1867,16 +1921,19 @@
         <v>0</v>
       </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1937,41 +1994,44 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>14100</v>
       </c>
-      <c r="G29" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I29" s="3">
         <v>-800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-1000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-1100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1300</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -1985,22 +2045,25 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>100</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2061,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2123,37 +2189,40 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>300</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
-        <v>-300</v>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>-300</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2185,8 +2254,11 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2194,61 +2266,64 @@
         <v>-900</v>
       </c>
       <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2309,8 +2384,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2318,128 +2396,134 @@
         <v>-900</v>
       </c>
       <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2462,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2486,70 +2571,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>39300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1600</v>
-      </c>
-      <c r="R41" s="3">
-        <v>1700</v>
       </c>
       <c r="S41" s="3">
         <v>1700</v>
       </c>
       <c r="T41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U41" s="3">
         <v>1600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2610,8 +2699,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2619,61 +2711,64 @@
         <v>500</v>
       </c>
       <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>400</v>
       </c>
       <c r="G43" s="3">
         <v>400</v>
       </c>
       <c r="H43" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="I43" s="3">
         <v>1600</v>
       </c>
       <c r="J43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K43" s="3">
         <v>2100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>700</v>
       </c>
       <c r="R43" s="3">
         <v>700</v>
       </c>
       <c r="S43" s="3">
+        <v>700</v>
+      </c>
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1300</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2698,8 +2793,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2734,8 +2829,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2749,117 +2847,123 @@
         <v>300</v>
       </c>
       <c r="G45" s="3">
+        <v>300</v>
+      </c>
+      <c r="H45" s="3">
         <v>67800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>71100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>73300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>53900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2700</v>
-      </c>
-      <c r="O46" s="3">
-        <v>3500</v>
       </c>
       <c r="P46" s="3">
         <v>3500</v>
       </c>
       <c r="Q46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R46" s="3">
         <v>3200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2875,8 +2979,8 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>200</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3">
         <v>200</v>
@@ -2893,8 +2997,8 @@
       <c r="M47" s="3">
         <v>200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
+      <c r="N47" s="3">
+        <v>200</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -2905,23 +3009,26 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3">
         <v>700</v>
-      </c>
-      <c r="S47" s="3">
-        <v>600</v>
       </c>
       <c r="T47" s="3">
         <v>600</v>
       </c>
       <c r="U47" s="3">
+        <v>600</v>
+      </c>
+      <c r="V47" s="3">
         <v>500</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2938,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>300</v>
@@ -2950,13 +3057,13 @@
         <v>300</v>
       </c>
       <c r="L48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2965,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3">
         <v>100</v>
@@ -2979,11 +3086,14 @@
       <c r="U48" s="3">
         <v>100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>100</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2997,37 +3107,37 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>10700</v>
       </c>
       <c r="J49" s="3">
         <v>10700</v>
       </c>
       <c r="K49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="L49" s="3">
         <v>10600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10300</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1500</v>
       </c>
       <c r="O49" s="3">
         <v>1500</v>
       </c>
       <c r="P49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q49" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>3200</v>
       </c>
       <c r="R49" s="3">
         <v>3200</v>
@@ -3036,16 +3146,19 @@
         <v>3200</v>
       </c>
       <c r="T49" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="U49" s="3">
         <v>3500</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3106,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3168,8 +3284,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3197,14 +3316,14 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>300</v>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M52" s="3">
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
@@ -3213,11 +3332,11 @@
         <v>400</v>
       </c>
       <c r="Q52" s="3">
+        <v>400</v>
+      </c>
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3230,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3292,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>84700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>59900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>60100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3378,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3402,46 +3531,47 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E57" s="3">
         <v>700</v>
       </c>
       <c r="F57" s="3">
+        <v>700</v>
+      </c>
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
@@ -3456,16 +3586,19 @@
         <v>100</v>
       </c>
       <c r="T57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>200</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3479,26 +3612,26 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>11400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3400</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3514,8 +3647,8 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3526,132 +3659,141 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>66400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>40900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>79200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>86800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>59000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3665,22 +3807,22 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2600</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2900</v>
       </c>
       <c r="K61" s="3">
         <v>2900</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3712,8 +3854,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3738,29 +3883,29 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
-      </c>
-      <c r="N62" s="3">
-        <v>300</v>
       </c>
       <c r="O62" s="3">
         <v>300</v>
       </c>
       <c r="P62" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>600</v>
-      </c>
-      <c r="R62" s="3">
-        <v>1000</v>
       </c>
       <c r="S62" s="3">
         <v>1000</v>
@@ -3769,13 +3914,16 @@
         <v>1000</v>
       </c>
       <c r="U62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V62" s="3">
         <v>900</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3836,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3898,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3960,70 +4114,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>500</v>
+      </c>
+      <c r="E66" s="3">
         <v>900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>80700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>89200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>61700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4046,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4108,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4170,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4232,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4294,70 +4464,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-77800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-76900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-76000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-75600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-87900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-82700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-79900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-76400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-73600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-70200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-58300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-29400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27500</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-27600</v>
       </c>
       <c r="T72" s="3">
         <v>-27600</v>
       </c>
       <c r="U72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="V72" s="3">
         <v>-27400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4418,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4480,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4542,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-9400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3200</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>3100</v>
       </c>
       <c r="R76" s="3">
         <v>3100</v>
       </c>
       <c r="S76" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="T76" s="3">
         <v>2800</v>
       </c>
       <c r="U76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V76" s="3">
         <v>2400</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4666,75 +4854,81 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4742,61 +4936,64 @@
         <v>-900</v>
       </c>
       <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4819,26 +5016,27 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -4846,19 +5044,19 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
@@ -4875,14 +5073,17 @@
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4943,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5005,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5067,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5129,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5191,47 +5404,50 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19500</v>
       </c>
-      <c r="G89" s="3">
-        <v>-63400</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-53000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5247,14 +5463,17 @@
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5277,8 +5496,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5304,25 +5524,25 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
@@ -5333,14 +5553,17 @@
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5401,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5463,8 +5689,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5475,34 +5704,34 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-18700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-200</v>
       </c>
       <c r="J94" s="3">
         <v>-200</v>
       </c>
       <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
         <v>48300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4400</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
@@ -5519,14 +5748,17 @@
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5549,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5575,8 +5808,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5611,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5673,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5735,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5797,46 +6039,49 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15700</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
@@ -5850,8 +6095,8 @@
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -5859,8 +6104,11 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5885,8 +6133,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5921,47 +6169,50 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-56400</v>
       </c>
-      <c r="G102" s="3">
-        <v>-61700</v>
-      </c>
       <c r="H102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I102" s="3">
         <v>2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-49000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>45000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5977,10 +6228,13 @@
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,118 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>700</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1000</v>
       </c>
       <c r="G8" s="3">
         <v>1000</v>
@@ -776,57 +780,60 @@
         <v>1000</v>
       </c>
       <c r="I8" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J8" s="3">
         <v>1300</v>
       </c>
       <c r="K8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E9" s="3">
         <v>700</v>
@@ -841,25 +848,25 @@
         <v>700</v>
       </c>
       <c r="I9" s="3">
+        <v>700</v>
+      </c>
+      <c r="J9" s="3">
         <v>1000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2900</v>
-      </c>
-      <c r="O9" s="3">
-        <v>900</v>
       </c>
       <c r="P9" s="3">
         <v>900</v>
@@ -868,42 +875,45 @@
         <v>900</v>
       </c>
       <c r="R9" s="3">
+        <v>900</v>
+      </c>
+      <c r="S9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>500</v>
-      </c>
-      <c r="U9" s="3">
-        <v>1000</v>
       </c>
       <c r="V9" s="3">
         <v>1000</v>
       </c>
       <c r="W9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
         <v>300</v>
       </c>
       <c r="H10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I10" s="3">
         <v>400</v>
@@ -915,43 +925,46 @@
         <v>400</v>
       </c>
       <c r="L10" s="3">
+        <v>400</v>
+      </c>
+      <c r="M10" s="3">
         <v>1300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +988,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1025,23 +1039,26 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>100</v>
-      </c>
-      <c r="U12" s="3">
-        <v>300</v>
       </c>
       <c r="V12" s="3">
         <v>300</v>
       </c>
       <c r="W12" s="3">
+        <v>300</v>
+      </c>
+      <c r="X12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,56 +1122,59 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>2700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>4700</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>4700</v>
       </c>
       <c r="N14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O14" s="3">
         <v>26200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1170,8 +1190,11 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1191,17 +1214,17 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1235,8 +1258,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1283,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2700</v>
       </c>
       <c r="H17" s="3">
         <v>2700</v>
       </c>
       <c r="I17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J17" s="3">
         <v>2800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1700</v>
       </c>
       <c r="K18" s="3">
         <v>-1700</v>
       </c>
       <c r="L18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M18" s="3">
         <v>-14300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-54700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,40 +1445,41 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>300</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>300</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1477,50 +1511,53 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E21" s="3">
         <v>-800</v>
       </c>
       <c r="F21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-54400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1542,43 +1579,46 @@
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
+      <c r="N22" s="3">
+        <v>100</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
@@ -1595,8 +1635,8 @@
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1607,82 +1647,88 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-54700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1714,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1732,13 +1778,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,56 +1851,59 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-54700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
@@ -1859,64 +1911,67 @@
         <v>0</v>
       </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="E27" s="3">
         <v>-900</v>
       </c>
       <c r="F27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-54700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
@@ -1924,16 +1979,19 @@
         <v>0</v>
       </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,44 +2055,47 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>14100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-1000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1300</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
@@ -2048,22 +2109,25 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>100</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
       <c r="V29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2191,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,40 +2259,43 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>-300</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>-300</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2257,73 +2327,79 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="E33" s="3">
         <v>-900</v>
       </c>
       <c r="F33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-54700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2463,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="E35" s="3">
         <v>-900</v>
       </c>
       <c r="F35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-54700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2632,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,8 +2658,9 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2581,64 +2668,67 @@
         <v>1400</v>
       </c>
       <c r="E41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>39300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1600</v>
-      </c>
-      <c r="S41" s="3">
-        <v>1700</v>
       </c>
       <c r="T41" s="3">
         <v>1700</v>
       </c>
       <c r="U41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V41" s="3">
         <v>1600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,73 +2792,79 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>500</v>
       </c>
       <c r="F43" s="3">
+        <v>500</v>
+      </c>
+      <c r="G43" s="3">
         <v>700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>400</v>
       </c>
       <c r="I43" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="J43" s="3">
         <v>1600</v>
       </c>
       <c r="K43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L43" s="3">
         <v>2100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>600</v>
-      </c>
-      <c r="R43" s="3">
-        <v>700</v>
       </c>
       <c r="S43" s="3">
         <v>700</v>
       </c>
       <c r="T43" s="3">
+        <v>700</v>
+      </c>
+      <c r="U43" s="3">
         <v>600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1300</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2796,8 +2892,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2832,13 +2928,16 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>300</v>
@@ -2850,125 +2949,131 @@
         <v>300</v>
       </c>
       <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
         <v>67800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>71100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>53900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2700</v>
-      </c>
-      <c r="P46" s="3">
-        <v>3500</v>
       </c>
       <c r="Q46" s="3">
         <v>3500</v>
       </c>
       <c r="R46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S46" s="3">
         <v>3200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>500</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -2982,8 +3087,8 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
-        <v>200</v>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
         <v>200</v>
@@ -3000,8 +3105,8 @@
       <c r="N47" s="3">
         <v>200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
+      <c r="O47" s="3">
+        <v>200</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
@@ -3012,23 +3117,26 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3">
         <v>700</v>
-      </c>
-      <c r="T47" s="3">
-        <v>600</v>
       </c>
       <c r="U47" s="3">
         <v>600</v>
       </c>
       <c r="V47" s="3">
+        <v>600</v>
+      </c>
+      <c r="W47" s="3">
         <v>500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3048,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
@@ -3060,13 +3168,13 @@
         <v>300</v>
       </c>
       <c r="M48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -3075,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>100</v>
@@ -3089,11 +3197,14 @@
       <c r="V48" s="3">
         <v>100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>100</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3110,37 +3221,37 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10900</v>
-      </c>
-      <c r="J49" s="3">
-        <v>10700</v>
       </c>
       <c r="K49" s="3">
         <v>10700</v>
       </c>
       <c r="L49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="M49" s="3">
         <v>10600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10300</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1500</v>
       </c>
       <c r="P49" s="3">
         <v>1500</v>
       </c>
       <c r="Q49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R49" s="3">
         <v>2600</v>
-      </c>
-      <c r="R49" s="3">
-        <v>3200</v>
       </c>
       <c r="S49" s="3">
         <v>3200</v>
@@ -3149,16 +3260,19 @@
         <v>3200</v>
       </c>
       <c r="U49" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="V49" s="3">
         <v>3500</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3336,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3404,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3319,14 +3439,14 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>300</v>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N52" s="3">
         <v>300</v>
       </c>
       <c r="O52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
@@ -3335,11 +3455,11 @@
         <v>400</v>
       </c>
       <c r="R52" s="3">
+        <v>400</v>
+      </c>
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3352,8 +3472,11 @@
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3540,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>59900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>60100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3636,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,49 +3662,50 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>700</v>
       </c>
       <c r="F57" s="3">
         <v>700</v>
       </c>
       <c r="G57" s="3">
+        <v>700</v>
+      </c>
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
@@ -3589,16 +3720,19 @@
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>200</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3615,26 +3749,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>11400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3400</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3650,8 +3784,8 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3662,8 +3796,11 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3671,129 +3808,135 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>66400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>40900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>51600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>79200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>86800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>59000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>55700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>58900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3810,22 +3953,22 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2600</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2900</v>
       </c>
       <c r="L61" s="3">
         <v>2900</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -3857,8 +4000,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3886,29 +4032,29 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
-      </c>
-      <c r="O62" s="3">
-        <v>300</v>
       </c>
       <c r="P62" s="3">
         <v>300</v>
       </c>
       <c r="Q62" s="3">
+        <v>300</v>
+      </c>
+      <c r="R62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
-      </c>
-      <c r="S62" s="3">
-        <v>1000</v>
       </c>
       <c r="T62" s="3">
         <v>1000</v>
@@ -3917,13 +4063,16 @@
         <v>1000</v>
       </c>
       <c r="V62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4136,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4204,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4272,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>700</v>
+      </c>
+      <c r="E66" s="3">
         <v>500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>80700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>89200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4368,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4434,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4502,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4570,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4638,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-78800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-77800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-76900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-76000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-75600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-87900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-82700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-76400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-73600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-70200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-58300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-28200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27500</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-27600</v>
       </c>
       <c r="U72" s="3">
         <v>-27600</v>
       </c>
       <c r="V72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="W72" s="3">
         <v>-27400</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4774,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4842,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,8 +4910,11 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4736,64 +4922,67 @@
         <v>2100</v>
       </c>
       <c r="E76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F76" s="3">
         <v>2000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-9400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3200</v>
-      </c>
-      <c r="R76" s="3">
-        <v>3100</v>
       </c>
       <c r="S76" s="3">
         <v>3100</v>
       </c>
       <c r="T76" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="U76" s="3">
         <v>2800</v>
       </c>
       <c r="V76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W76" s="3">
         <v>2400</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5046,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="E81" s="3">
         <v>-900</v>
       </c>
       <c r="F81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-54700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5215,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5026,20 +5225,20 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
@@ -5047,19 +5246,19 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
@@ -5076,14 +5275,17 @@
       <c r="U83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5349,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5417,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5485,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5553,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,50 +5621,53 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-53000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5466,14 +5683,17 @@
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,13 +5717,14 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -5527,25 +5748,25 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>8</v>
@@ -5556,14 +5777,17 @@
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5851,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,13 +5919,16 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -5707,34 +5937,34 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-18700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-200</v>
       </c>
       <c r="K94" s="3">
         <v>-200</v>
       </c>
       <c r="L94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M94" s="3">
         <v>48300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4400</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
@@ -5751,14 +5981,17 @@
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6015,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5811,8 +6045,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5847,8 +6081,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6149,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6217,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,49 +6285,52 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
@@ -6098,8 +6344,8 @@
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -6107,8 +6353,11 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6136,8 +6385,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6172,50 +6421,53 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-56400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-49000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>45000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6231,10 +6483,13 @@
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,111 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -768,13 +772,13 @@
         <v>700</v>
       </c>
       <c r="E8" s="3">
+        <v>700</v>
+      </c>
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1000</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
@@ -783,60 +787,63 @@
         <v>1000</v>
       </c>
       <c r="J8" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="K8" s="3">
         <v>1300</v>
       </c>
       <c r="L8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
         <v>600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>700</v>
       </c>
       <c r="F9" s="3">
         <v>700</v>
@@ -851,25 +858,25 @@
         <v>700</v>
       </c>
       <c r="J9" s="3">
+        <v>700</v>
+      </c>
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2900</v>
-      </c>
-      <c r="P9" s="3">
-        <v>900</v>
       </c>
       <c r="Q9" s="3">
         <v>900</v>
@@ -878,45 +885,48 @@
         <v>900</v>
       </c>
       <c r="S9" s="3">
+        <v>900</v>
+      </c>
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>500</v>
-      </c>
-      <c r="V9" s="3">
-        <v>1000</v>
       </c>
       <c r="W9" s="3">
         <v>1000</v>
       </c>
       <c r="X9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>300</v>
       </c>
       <c r="I10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J10" s="3">
         <v>400</v>
@@ -928,43 +938,46 @@
         <v>400</v>
       </c>
       <c r="M10" s="3">
+        <v>400</v>
+      </c>
+      <c r="N10" s="3">
         <v>1300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -989,8 +1002,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,23 +1056,26 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="3">
         <v>300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>100</v>
-      </c>
-      <c r="V12" s="3">
-        <v>300</v>
       </c>
       <c r="W12" s="3">
         <v>300</v>
       </c>
       <c r="X12" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,59 +1142,62 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J14" s="3">
         <v>2700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
-        <v>4700</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>4700</v>
       </c>
       <c r="O14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P14" s="3">
         <v>26200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1193,8 +1213,11 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1217,17 +1240,17 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1261,8 +1284,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,144 +1310,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2700</v>
       </c>
       <c r="I17" s="3">
         <v>2700</v>
       </c>
       <c r="J17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K17" s="3">
         <v>2800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1700</v>
       </c>
       <c r="L18" s="3">
         <v>-1700</v>
       </c>
       <c r="M18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N18" s="3">
         <v>-14300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-54700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,43 +1479,44 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
+        <v>-300</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>300</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>300</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1514,53 +1548,56 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-800</v>
       </c>
       <c r="F21" s="3">
         <v>-800</v>
       </c>
       <c r="G21" s="3">
-        <v>-1200</v>
+        <v>-800</v>
       </c>
       <c r="H21" s="3">
-        <v>-1400</v>
+        <v>-900</v>
       </c>
       <c r="I21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-54400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1582,46 +1619,49 @@
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
+      <c r="O22" s="3">
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
@@ -1638,8 +1678,8 @@
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1650,76 +1690,82 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-54700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1727,11 +1773,11 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1763,16 +1809,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1781,13 +1827,16 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,59 +1903,62 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-54700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
@@ -1914,67 +1966,70 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-900</v>
       </c>
       <c r="F27" s="3">
         <v>-900</v>
       </c>
       <c r="G27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
@@ -1982,16 +2037,19 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2116,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2067,38 +2128,38 @@
         <v>-100</v>
       </c>
       <c r="E29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="3">
         <v>100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>14100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-1000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1300</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
@@ -2112,22 +2173,25 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>100</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2258,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,43 +2329,46 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H32" s="3">
-        <v>200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
+        <v>300</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>-300</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>-300</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2330,76 +2400,82 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-900</v>
       </c>
       <c r="F33" s="3">
         <v>-900</v>
       </c>
       <c r="G33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,149 +2542,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-900</v>
       </c>
       <c r="F35" s="3">
         <v>-900</v>
       </c>
       <c r="G35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2718,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,76 +2745,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1400</v>
+        <v>5100</v>
       </c>
       <c r="E41" s="3">
         <v>1400</v>
       </c>
       <c r="F41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G41" s="3">
         <v>1900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>39300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1600</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1700</v>
       </c>
       <c r="U41" s="3">
         <v>1700</v>
       </c>
       <c r="V41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W41" s="3">
         <v>1600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2795,76 +2885,82 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>500</v>
       </c>
       <c r="F43" s="3">
         <v>500</v>
       </c>
       <c r="G43" s="3">
+        <v>500</v>
+      </c>
+      <c r="H43" s="3">
         <v>700</v>
-      </c>
-      <c r="H43" s="3">
-        <v>400</v>
       </c>
       <c r="I43" s="3">
         <v>400</v>
       </c>
       <c r="J43" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="K43" s="3">
         <v>1600</v>
       </c>
       <c r="L43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M43" s="3">
         <v>2100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
-      </c>
-      <c r="S43" s="3">
-        <v>700</v>
       </c>
       <c r="T43" s="3">
         <v>700</v>
       </c>
       <c r="U43" s="3">
+        <v>700</v>
+      </c>
+      <c r="V43" s="3">
         <v>600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1300</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2895,8 +2991,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2931,16 +3027,19 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
@@ -2952,131 +3051,137 @@
         <v>300</v>
       </c>
       <c r="I45" s="3">
+        <v>300</v>
+      </c>
+      <c r="J45" s="3">
         <v>67800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1600</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>71100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>73300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>48900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>53900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>3500</v>
       </c>
       <c r="R46" s="3">
         <v>3500</v>
       </c>
       <c r="S46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T46" s="3">
         <v>3200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>500</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
+      <c r="E47" s="3">
+        <v>500</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -3090,8 +3195,8 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
-        <v>200</v>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>200</v>
@@ -3108,8 +3213,8 @@
       <c r="O47" s="3">
         <v>200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
+      <c r="P47" s="3">
+        <v>200</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
@@ -3120,23 +3225,26 @@
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U47" s="3">
         <v>700</v>
-      </c>
-      <c r="U47" s="3">
-        <v>600</v>
       </c>
       <c r="V47" s="3">
         <v>600</v>
       </c>
       <c r="W47" s="3">
+        <v>600</v>
+      </c>
+      <c r="X47" s="3">
         <v>500</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3159,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
@@ -3171,13 +3279,13 @@
         <v>300</v>
       </c>
       <c r="N48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>200</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -3186,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T48" s="3">
         <v>100</v>
@@ -3200,16 +3308,19 @@
       <c r="W48" s="3">
         <v>100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>382400</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -3224,37 +3335,37 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10900</v>
-      </c>
-      <c r="K49" s="3">
-        <v>10700</v>
       </c>
       <c r="L49" s="3">
         <v>10700</v>
       </c>
       <c r="M49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="N49" s="3">
         <v>10600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1500</v>
       </c>
       <c r="Q49" s="3">
         <v>1500</v>
       </c>
       <c r="R49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S49" s="3">
         <v>2600</v>
-      </c>
-      <c r="S49" s="3">
-        <v>3200</v>
       </c>
       <c r="T49" s="3">
         <v>3200</v>
@@ -3263,16 +3374,19 @@
         <v>3200</v>
       </c>
       <c r="V49" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="W49" s="3">
         <v>3500</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3453,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,13 +3524,16 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>61500</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -3442,14 +3562,14 @@
       <c r="M52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="3">
-        <v>300</v>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
       </c>
       <c r="P52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q52" s="3">
         <v>400</v>
@@ -3458,11 +3578,11 @@
         <v>400</v>
       </c>
       <c r="S52" s="3">
+        <v>400</v>
+      </c>
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3475,8 +3595,11 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,76 +3666,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>453900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>84700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>59900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>60100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3766,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,52 +3793,53 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>700</v>
       </c>
       <c r="G57" s="3">
         <v>700</v>
       </c>
       <c r="H57" s="3">
+        <v>700</v>
+      </c>
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
@@ -3723,16 +3854,19 @@
         <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3752,26 +3886,26 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>11400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3400</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3787,8 +3921,8 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3799,8 +3933,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3811,132 +3948,138 @@
         <v>0</v>
       </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>66400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>58400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>40900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>79200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>86800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>58900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3956,22 +4099,22 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2900</v>
       </c>
       <c r="M61" s="3">
         <v>2900</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -4003,8 +4146,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4035,29 +4181,29 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
-      </c>
-      <c r="P62" s="3">
-        <v>300</v>
       </c>
       <c r="Q62" s="3">
         <v>300</v>
       </c>
       <c r="R62" s="3">
+        <v>300</v>
+      </c>
+      <c r="S62" s="3">
         <v>500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1000</v>
       </c>
       <c r="U62" s="3">
         <v>1000</v>
@@ -4066,13 +4212,16 @@
         <v>1000</v>
       </c>
       <c r="W62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X62" s="3">
         <v>900</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4288,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4359,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,76 +4430,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E66" s="3">
         <v>700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>89200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4530,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4599,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4670,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4741,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,76 +4812,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-182200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-78800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-77800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-76900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-76000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-75600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-87900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-82700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-76400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-73600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-70200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-58300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-29400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-28200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-27500</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-27600</v>
       </c>
       <c r="V72" s="3">
         <v>-27600</v>
       </c>
       <c r="W72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="X72" s="3">
         <v>-27400</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4954,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5025,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,76 +5096,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2100</v>
+        <v>452500</v>
       </c>
       <c r="E76" s="3">
         <v>2100</v>
       </c>
       <c r="F76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G76" s="3">
         <v>2000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-9400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-4500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3200</v>
-      </c>
-      <c r="S76" s="3">
-        <v>3100</v>
       </c>
       <c r="T76" s="3">
         <v>3100</v>
       </c>
       <c r="U76" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="V76" s="3">
         <v>2800</v>
       </c>
       <c r="W76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X76" s="3">
         <v>2400</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,149 +5238,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-900</v>
       </c>
       <c r="F81" s="3">
         <v>-900</v>
       </c>
       <c r="G81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,8 +5414,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5228,20 +5427,20 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -5249,19 +5448,19 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
@@ -5278,14 +5477,17 @@
       <c r="V83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5554,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5625,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5696,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5767,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,53 +5838,56 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-53000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5686,14 +5903,17 @@
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,16 +5938,17 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -5751,25 +5972,25 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
@@ -5780,14 +6001,17 @@
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6078,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,17 +6149,20 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-405800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -5940,34 +6170,34 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-18700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-200</v>
       </c>
       <c r="L94" s="3">
         <v>-200</v>
       </c>
       <c r="M94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N94" s="3">
         <v>48300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
@@ -5984,14 +6214,17 @@
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,8 +6249,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6048,8 +6282,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6084,8 +6318,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6389,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6460,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,52 +6531,55 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>411100</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>15700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
@@ -6347,8 +6593,8 @@
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -6356,8 +6602,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6388,8 +6637,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6424,53 +6673,56 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-56400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-49000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>45000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6486,10 +6738,13 @@
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,139 +656,142 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E8" s="3">
         <v>10800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>700</v>
       </c>
       <c r="F8" s="3">
         <v>700</v>
       </c>
       <c r="G8" s="3">
+        <v>700</v>
+      </c>
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1000</v>
       </c>
       <c r="J8" s="3">
         <v>1000</v>
@@ -797,52 +800,55 @@
         <v>1000</v>
       </c>
       <c r="L8" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="M8" s="3">
         <v>1300</v>
       </c>
       <c r="N8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -850,13 +856,13 @@
         <v>400</v>
       </c>
       <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>700</v>
       </c>
       <c r="H9" s="3">
         <v>700</v>
@@ -871,25 +877,25 @@
         <v>700</v>
       </c>
       <c r="L9" s="3">
+        <v>700</v>
+      </c>
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2900</v>
-      </c>
-      <c r="R9" s="3">
-        <v>900</v>
       </c>
       <c r="S9" s="3">
         <v>900</v>
@@ -898,51 +904,54 @@
         <v>900</v>
       </c>
       <c r="U9" s="3">
+        <v>900</v>
+      </c>
+      <c r="V9" s="3">
         <v>500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>500</v>
-      </c>
-      <c r="X9" s="3">
-        <v>1000</v>
       </c>
       <c r="Y9" s="3">
         <v>1000</v>
       </c>
       <c r="Z9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E10" s="3">
         <v>10400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
       </c>
       <c r="I10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J10" s="3">
         <v>300</v>
       </c>
       <c r="K10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L10" s="3">
         <v>400</v>
@@ -954,43 +963,46 @@
         <v>400</v>
       </c>
       <c r="O10" s="3">
+        <v>400</v>
+      </c>
+      <c r="P10" s="3">
         <v>1300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1017,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1076,23 +1089,26 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>300</v>
       </c>
       <c r="Y12" s="3">
         <v>300</v>
       </c>
       <c r="Z12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,65 +1181,68 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>84900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L14" s="3">
-        <v>300</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
-        <v>4700</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>4700</v>
       </c>
       <c r="Q14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="R14" s="3">
         <v>26200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1239,8 +1258,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1269,17 +1291,17 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1313,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>750300</v>
+      </c>
+      <c r="E17" s="3">
         <v>-94100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2700</v>
       </c>
       <c r="K17" s="3">
         <v>2700</v>
       </c>
       <c r="L17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M17" s="3">
         <v>2800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>57100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-734500</v>
+      </c>
+      <c r="E18" s="3">
         <v>104900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1700</v>
       </c>
       <c r="N18" s="3">
         <v>-1700</v>
       </c>
       <c r="O18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="P18" s="3">
         <v>-14300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-54700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-800</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,49 +1546,50 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
-        <v>300</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O20" s="3">
         <v>300</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1588,59 +1621,62 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-734500</v>
+      </c>
+      <c r="E21" s="3">
         <v>104900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-54400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1662,8 +1698,11 @@
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1676,38 +1715,38 @@
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
       </c>
       <c r="O22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
+      <c r="Q22" s="3">
+        <v>100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
@@ -1724,8 +1763,8 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1736,100 +1775,106 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-734300</v>
+      </c>
+      <c r="E23" s="3">
         <v>105000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-103300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-54700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-800</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1861,16 +1906,16 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1879,13 +1924,16 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,65 +2006,68 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-734500</v>
+      </c>
+      <c r="E26" s="3">
         <v>104200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-103400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-54700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-700</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
@@ -2024,73 +2075,76 @@
         <v>0</v>
       </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-734500</v>
+      </c>
+      <c r="E27" s="3">
         <v>104300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-103400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900</v>
       </c>
       <c r="H27" s="3">
         <v>-900</v>
       </c>
       <c r="I27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-54700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
@@ -2098,16 +2152,19 @@
         <v>0</v>
       </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,44 +2249,44 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>-100</v>
       </c>
       <c r="G29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H29" s="3">
         <v>100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>14100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-1100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -2240,22 +2300,25 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>100</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
       <c r="Y29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,49 +2468,52 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
-        <v>300</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
-        <v>-300</v>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O32" s="3">
         <v>-300</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2476,82 +2545,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-734500</v>
+      </c>
+      <c r="E33" s="3">
         <v>104300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-103400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900</v>
       </c>
       <c r="H33" s="3">
         <v>-900</v>
       </c>
       <c r="I33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-54700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-734500</v>
+      </c>
+      <c r="E35" s="3">
         <v>104300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-103400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900</v>
       </c>
       <c r="H35" s="3">
         <v>-900</v>
       </c>
       <c r="I35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-54700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,82 +2918,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E41" s="3">
         <v>11100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1400</v>
       </c>
       <c r="G41" s="3">
         <v>1400</v>
       </c>
       <c r="H41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I41" s="3">
         <v>1900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>39300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1600</v>
-      </c>
-      <c r="V41" s="3">
-        <v>1700</v>
       </c>
       <c r="W41" s="3">
         <v>1700</v>
       </c>
       <c r="X41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y41" s="3">
         <v>1600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2981,82 +3070,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>500</v>
       </c>
       <c r="H43" s="3">
         <v>500</v>
       </c>
       <c r="I43" s="3">
+        <v>500</v>
+      </c>
+      <c r="J43" s="3">
         <v>700</v>
-      </c>
-      <c r="J43" s="3">
-        <v>400</v>
       </c>
       <c r="K43" s="3">
         <v>400</v>
       </c>
       <c r="L43" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="M43" s="3">
         <v>1600</v>
       </c>
       <c r="N43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O43" s="3">
         <v>2100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>600</v>
-      </c>
-      <c r="U43" s="3">
-        <v>700</v>
       </c>
       <c r="V43" s="3">
         <v>700</v>
       </c>
       <c r="W43" s="3">
+        <v>700</v>
+      </c>
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1300</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3093,8 +3188,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3129,22 +3224,25 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E45" s="3">
         <v>27100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>300</v>
@@ -3156,134 +3254,140 @@
         <v>300</v>
       </c>
       <c r="K45" s="3">
+        <v>300</v>
+      </c>
+      <c r="L45" s="3">
         <v>67800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E46" s="3">
         <v>40000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>71100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>73300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>48700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>53900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2700</v>
-      </c>
-      <c r="S46" s="3">
-        <v>3500</v>
       </c>
       <c r="T46" s="3">
         <v>3500</v>
       </c>
       <c r="U46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V46" s="3">
         <v>3200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>500</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
         <v>500</v>
@@ -3291,8 +3395,8 @@
       <c r="F47" s="3">
         <v>500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
+      <c r="G47" s="3">
+        <v>500</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -3306,8 +3410,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>200</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>200</v>
@@ -3324,8 +3428,8 @@
       <c r="Q47" s="3">
         <v>200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
+      <c r="R47" s="3">
+        <v>200</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
@@ -3336,23 +3440,26 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W47" s="3">
         <v>700</v>
-      </c>
-      <c r="W47" s="3">
-        <v>600</v>
       </c>
       <c r="X47" s="3">
         <v>600</v>
       </c>
       <c r="Y47" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z47" s="3">
         <v>500</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3381,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
@@ -3393,13 +3500,13 @@
         <v>300</v>
       </c>
       <c r="P48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q48" s="3">
         <v>200</v>
       </c>
       <c r="R48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -3408,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V48" s="3">
         <v>100</v>
@@ -3422,11 +3529,14 @@
       <c r="Y48" s="3">
         <v>100</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3434,11 +3544,11 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>382400</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -3452,37 +3562,37 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>10700</v>
       </c>
       <c r="N49" s="3">
         <v>10700</v>
       </c>
       <c r="O49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="P49" s="3">
         <v>10600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10300</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1500</v>
       </c>
       <c r="S49" s="3">
         <v>1500</v>
       </c>
       <c r="T49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U49" s="3">
         <v>2600</v>
-      </c>
-      <c r="U49" s="3">
-        <v>3200</v>
       </c>
       <c r="V49" s="3">
         <v>3200</v>
@@ -3491,16 +3601,19 @@
         <v>3200</v>
       </c>
       <c r="X49" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="Y49" s="3">
         <v>3500</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,20 +3763,23 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2400600</v>
+      </c>
+      <c r="E52" s="3">
         <v>3032500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>61500</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3688,14 +3807,14 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
-        <v>300</v>
+      <c r="P52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q52" s="3">
         <v>300</v>
       </c>
       <c r="R52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
@@ -3704,11 +3823,11 @@
         <v>400</v>
       </c>
       <c r="U52" s="3">
+        <v>400</v>
+      </c>
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3721,8 +3840,11 @@
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2431800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3073000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>453900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>84700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>59900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>60100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7500</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,58 +4054,59 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
-        <v>300</v>
-      </c>
       <c r="H57" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I57" s="3">
         <v>700</v>
       </c>
       <c r="J57" s="3">
+        <v>700</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
@@ -3991,16 +4121,19 @@
         <v>100</v>
       </c>
       <c r="X57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4026,26 +4159,26 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>11400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4061,8 +4194,8 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4073,8 +4206,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4091,138 +4227,144 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>66400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>58400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>40900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>51600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>79200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>86800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>55700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>58900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4200</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4248,22 +4390,22 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2600</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2900</v>
       </c>
       <c r="O61" s="3">
         <v>2900</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -4295,8 +4437,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4333,29 +4478,29 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>500</v>
-      </c>
-      <c r="R62" s="3">
-        <v>300</v>
       </c>
       <c r="S62" s="3">
         <v>300</v>
       </c>
       <c r="T62" s="3">
+        <v>300</v>
+      </c>
+      <c r="U62" s="3">
         <v>500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>600</v>
-      </c>
-      <c r="V62" s="3">
-        <v>1000</v>
       </c>
       <c r="W62" s="3">
         <v>1000</v>
@@ -4364,13 +4509,16 @@
         <v>1000</v>
       </c>
       <c r="Y62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z62" s="3">
         <v>900</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>80700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>89200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>62100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4915,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-812400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-77900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-182200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-78800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-77800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-76900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-76000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-75600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-87900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-82700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-79900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-76400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-73600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-70200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-58300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-29400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-28200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-27600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-27500</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-27600</v>
       </c>
       <c r="X72" s="3">
         <v>-27600</v>
       </c>
       <c r="Y72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-27400</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2419000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3068400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>452500</v>
-      </c>
-      <c r="F76" s="3">
-        <v>2100</v>
       </c>
       <c r="G76" s="3">
         <v>2100</v>
       </c>
       <c r="H76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I76" s="3">
         <v>2000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-9400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-4500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3200</v>
-      </c>
-      <c r="U76" s="3">
-        <v>3100</v>
       </c>
       <c r="V76" s="3">
         <v>3100</v>
       </c>
       <c r="W76" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="X76" s="3">
         <v>2800</v>
       </c>
       <c r="Y76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Z76" s="3">
         <v>2400</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-734500</v>
+      </c>
+      <c r="E81" s="3">
         <v>104300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-103400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900</v>
       </c>
       <c r="H81" s="3">
         <v>-900</v>
       </c>
       <c r="I81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-54700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5641,11 +5839,11 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -5653,19 +5851,19 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
@@ -5682,14 +5880,17 @@
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,59 +6271,62 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-53000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6126,14 +6342,17 @@
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6171,11 +6391,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -6199,25 +6419,25 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
@@ -6228,14 +6448,17 @@
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,23 +6608,26 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2498200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-405800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -6406,34 +6635,34 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-18700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-200</v>
       </c>
       <c r="N94" s="3">
         <v>-200</v>
       </c>
       <c r="O94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P94" s="3">
         <v>48300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
@@ -6450,14 +6679,17 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6522,8 +6755,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6558,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,58 +7022,61 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2510500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>411100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>15700</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>8</v>
@@ -6845,8 +7090,8 @@
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -6854,8 +7099,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6892,8 +7140,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6928,59 +7176,62 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E102" s="3">
         <v>6100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-56400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-49000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>45000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6996,10 +7247,13 @@
       <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>SBET</t>
   </si>
@@ -656,145 +656,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E8" s="3">
         <v>15800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>700</v>
       </c>
       <c r="G8" s="3">
         <v>700</v>
       </c>
       <c r="H8" s="3">
+        <v>700</v>
+      </c>
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>900</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1000</v>
       </c>
       <c r="K8" s="3">
         <v>1000</v>
@@ -803,52 +807,55 @@
         <v>1000</v>
       </c>
       <c r="M8" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="N8" s="3">
         <v>1300</v>
       </c>
       <c r="O8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -859,13 +866,13 @@
         <v>400</v>
       </c>
       <c r="F9" s="3">
+        <v>400</v>
+      </c>
+      <c r="G9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>700</v>
       </c>
       <c r="I9" s="3">
         <v>700</v>
@@ -880,25 +887,25 @@
         <v>700</v>
       </c>
       <c r="M9" s="3">
+        <v>700</v>
+      </c>
+      <c r="N9" s="3">
         <v>1000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2900</v>
-      </c>
-      <c r="S9" s="3">
-        <v>900</v>
       </c>
       <c r="T9" s="3">
         <v>900</v>
@@ -907,54 +914,57 @@
         <v>900</v>
       </c>
       <c r="V9" s="3">
+        <v>900</v>
+      </c>
+      <c r="W9" s="3">
         <v>500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>500</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>1000</v>
       </c>
       <c r="Z9" s="3">
         <v>1000</v>
       </c>
       <c r="AA9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB9" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E10" s="3">
         <v>15400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>200</v>
       </c>
       <c r="J10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K10" s="3">
         <v>300</v>
       </c>
       <c r="L10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M10" s="3">
         <v>400</v>
@@ -966,43 +976,46 @@
         <v>400</v>
       </c>
       <c r="P10" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1043,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1092,23 +1106,26 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X12" s="3">
         <v>300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>100</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>300</v>
       </c>
       <c r="Z12" s="3">
         <v>300</v>
       </c>
       <c r="AA12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1201,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1195,57 +1215,57 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>84900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
-        <v>4700</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>4700</v>
       </c>
       <c r="R14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S14" s="3">
         <v>26200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1261,8 +1281,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1294,17 +1317,17 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>100</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1338,8 +1361,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1390,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>696600</v>
+      </c>
+      <c r="E17" s="3">
         <v>750300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-94100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2700</v>
       </c>
       <c r="L17" s="3">
         <v>2700</v>
       </c>
       <c r="M17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N17" s="3">
         <v>2800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>57100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-684600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-734500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>104900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1700</v>
       </c>
       <c r="O18" s="3">
         <v>-1700</v>
       </c>
       <c r="P18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-54700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-200</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,52 +1580,53 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>300</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>300</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1624,62 +1658,65 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-684600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-734500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>104900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-54400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1701,8 +1738,11 @@
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1718,38 +1758,38 @@
       <c r="G22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
+      <c r="R22" s="3">
+        <v>100</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
@@ -1766,8 +1806,8 @@
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1778,106 +1818,112 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-684400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-734300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>105000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-103300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-800</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
       <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1909,16 +1955,16 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1927,13 +1973,16 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,68 +2058,71 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-685600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-734500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>104200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-103400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-54700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-700</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
@@ -2078,76 +2130,79 @@
         <v>0</v>
       </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
       <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-685600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-734500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>104300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-103400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-900</v>
       </c>
       <c r="I27" s="3">
         <v>-900</v>
       </c>
       <c r="J27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-54700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
@@ -2155,16 +2210,19 @@
         <v>0</v>
       </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2298,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,44 +2313,44 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>-100</v>
       </c>
       <c r="H29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I29" s="3">
         <v>100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>14100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1300</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2303,22 +2364,25 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
       <c r="Z29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2458,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,52 +2538,55 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>-300</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>-300</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2548,85 +2618,91 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-685600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-734500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>104300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-103400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-900</v>
       </c>
       <c r="I33" s="3">
         <v>-900</v>
       </c>
       <c r="J33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-54700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2778,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-685600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-734500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>104300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-103400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-900</v>
       </c>
       <c r="I35" s="3">
         <v>-900</v>
       </c>
       <c r="J35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-54700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2975,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3005,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E41" s="3">
         <v>28500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1400</v>
       </c>
       <c r="H41" s="3">
         <v>1400</v>
       </c>
       <c r="I41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1600</v>
-      </c>
-      <c r="W41" s="3">
-        <v>1700</v>
       </c>
       <c r="X41" s="3">
         <v>1700</v>
       </c>
       <c r="Y41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z41" s="3">
         <v>1600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,85 +3163,91 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
-      </c>
-      <c r="H43" s="3">
-        <v>500</v>
       </c>
       <c r="I43" s="3">
         <v>500</v>
       </c>
       <c r="J43" s="3">
+        <v>500</v>
+      </c>
+      <c r="K43" s="3">
         <v>700</v>
-      </c>
-      <c r="K43" s="3">
-        <v>400</v>
       </c>
       <c r="L43" s="3">
         <v>400</v>
       </c>
       <c r="M43" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="N43" s="3">
         <v>1600</v>
       </c>
       <c r="O43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P43" s="3">
         <v>2100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>600</v>
-      </c>
-      <c r="V43" s="3">
-        <v>700</v>
       </c>
       <c r="W43" s="3">
         <v>700</v>
       </c>
       <c r="X43" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1300</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3191,8 +3287,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3227,25 +3323,28 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
@@ -3257,140 +3356,146 @@
         <v>300</v>
       </c>
       <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>67800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E46" s="3">
         <v>31200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>71100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>73300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>48900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>53900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2700</v>
-      </c>
-      <c r="T46" s="3">
-        <v>3500</v>
       </c>
       <c r="U46" s="3">
         <v>3500</v>
       </c>
       <c r="V46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="W46" s="3">
         <v>3200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
-        <v>500</v>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
         <v>500</v>
@@ -3398,8 +3503,8 @@
       <c r="G47" s="3">
         <v>500</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
+      <c r="H47" s="3">
+        <v>500</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -3413,8 +3518,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>200</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>200</v>
@@ -3431,8 +3536,8 @@
       <c r="R47" s="3">
         <v>200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
+      <c r="S47" s="3">
+        <v>200</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
@@ -3443,28 +3548,31 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X47" s="3">
         <v>700</v>
-      </c>
-      <c r="X47" s="3">
-        <v>600</v>
       </c>
       <c r="Y47" s="3">
         <v>600</v>
       </c>
       <c r="Z47" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA47" s="3">
         <v>500</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
@@ -3491,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
@@ -3503,13 +3611,13 @@
         <v>300</v>
       </c>
       <c r="Q48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>200</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -3518,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W48" s="3">
         <v>100</v>
@@ -3532,11 +3640,14 @@
       <c r="Z48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3547,11 +3658,11 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>382400</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -3565,37 +3676,37 @@
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10900</v>
-      </c>
-      <c r="N49" s="3">
-        <v>10700</v>
       </c>
       <c r="O49" s="3">
         <v>10700</v>
       </c>
       <c r="P49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="Q49" s="3">
         <v>10600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10300</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1500</v>
       </c>
       <c r="T49" s="3">
         <v>1500</v>
       </c>
       <c r="U49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V49" s="3">
         <v>2600</v>
-      </c>
-      <c r="V49" s="3">
-        <v>3200</v>
       </c>
       <c r="W49" s="3">
         <v>3200</v>
@@ -3604,16 +3715,19 @@
         <v>3200</v>
       </c>
       <c r="Y49" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="Z49" s="3">
         <v>3500</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3803,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,23 +3883,26 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1726000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2400600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3032500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61500</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3810,14 +3930,14 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
-        <v>300</v>
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R52" s="3">
         <v>300</v>
       </c>
       <c r="S52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
@@ -3826,11 +3946,11 @@
         <v>400</v>
       </c>
       <c r="V52" s="3">
+        <v>400</v>
+      </c>
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3843,8 +3963,11 @@
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4043,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2431800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3073000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>453900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>84700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>59900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>60100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>65000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4155,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,61 +4185,62 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>700</v>
       </c>
       <c r="J57" s="3">
         <v>700</v>
       </c>
       <c r="K57" s="3">
+        <v>700</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T57" s="3">
         <v>200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
@@ -4124,16 +4255,19 @@
         <v>100</v>
       </c>
       <c r="Y57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4162,26 +4296,26 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>11400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3400</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4197,8 +4331,8 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4209,13 +4343,16 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -4230,141 +4367,147 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>66400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>58400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>40900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>38800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>51600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>12700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>79200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>86800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>59000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>55700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>58900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4200</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4393,22 +4536,22 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>1400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2600</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2900</v>
       </c>
       <c r="P61" s="3">
         <v>2900</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -4440,8 +4583,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4481,29 +4627,29 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>500</v>
-      </c>
-      <c r="S62" s="3">
-        <v>300</v>
       </c>
       <c r="T62" s="3">
         <v>300</v>
       </c>
       <c r="U62" s="3">
+        <v>300</v>
+      </c>
+      <c r="V62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>600</v>
-      </c>
-      <c r="W62" s="3">
-        <v>1000</v>
       </c>
       <c r="X62" s="3">
         <v>1000</v>
@@ -4512,13 +4658,16 @@
         <v>1000</v>
       </c>
       <c r="Z62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA62" s="3">
         <v>900</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4743,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4823,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +4903,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E66" s="3">
         <v>12700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>80700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>89200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>62100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5015,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5093,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5173,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5253,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5333,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1498000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-812400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-77900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-182200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-78800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-77800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-76900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-76000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-75600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-87900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-82700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-79900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-76400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-73600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-70200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-58300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-30400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-29400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-28200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-27600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-27500</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-27600</v>
       </c>
       <c r="Y72" s="3">
         <v>-27600</v>
       </c>
       <c r="Z72" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-27400</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5493,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5573,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5653,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1738600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2419000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3068400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>452500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2100</v>
       </c>
       <c r="H76" s="3">
         <v>2100</v>
       </c>
       <c r="I76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J76" s="3">
         <v>2000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-9400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-4500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3200</v>
-      </c>
-      <c r="V76" s="3">
-        <v>3100</v>
       </c>
       <c r="W76" s="3">
         <v>3100</v>
       </c>
       <c r="X76" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="Y76" s="3">
         <v>2800</v>
       </c>
       <c r="Z76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AA76" s="3">
         <v>2400</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5813,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-685600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-734500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>104300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-103400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-900</v>
       </c>
       <c r="I81" s="3">
         <v>-900</v>
       </c>
       <c r="J81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-54700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6010,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5842,11 +6041,11 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -5854,19 +6053,19 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>8</v>
@@ -5883,14 +6082,17 @@
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6168,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6248,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6328,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6408,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,62 +6488,65 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-53000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6345,14 +6562,17 @@
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6600,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6394,11 +6615,11 @@
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -6422,25 +6643,25 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
       </c>
       <c r="R91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
@@ -6451,14 +6672,17 @@
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6758,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,26 +6838,29 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2498200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-405800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -6638,34 +6868,34 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-18700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-200</v>
       </c>
       <c r="O94" s="3">
         <v>-200</v>
       </c>
       <c r="P94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q94" s="3">
         <v>48300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
@@ -6682,14 +6912,17 @@
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6950,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6758,8 +6992,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6794,8 +7028,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7108,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7188,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,61 +7268,64 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E100" s="3">
         <v>76100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2510500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>411100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>15700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>8</v>
@@ -7093,8 +7339,8 @@
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -7102,8 +7348,11 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7143,8 +7392,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7179,62 +7428,65 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E102" s="3">
         <v>17400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-56400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-49000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>45000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7250,10 +7502,13 @@
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>
